--- a/benchmarks_tests/FINAL_Benchmarks_for_paper/PySCF_scaling_behavior_SAO.xlsx
+++ b/benchmarks_tests/FINAL_Benchmarks_for_paper/PySCF_scaling_behavior_SAO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manas/Documents/PyFock/benchmarks_tests/FINAL_Benchmarks_for_paper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E07548-E7D0-2A4D-9E15-756DDFF3DB12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF0ED26-A868-1C4B-AE76-794686B32011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16840" xr2:uid="{580CF0B2-FD39-1547-AD8E-82680C382266}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16800" activeTab="1" xr2:uid="{580CF0B2-FD39-1547-AD8E-82680C382266}"/>
   </bookViews>
   <sheets>
     <sheet name="def2-SVP" sheetId="1" r:id="rId1"/>
@@ -304,28 +304,28 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>0.346481050900183</c:v>
+                  <c:v>0.32148105090018297</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.3363337981669832</c:v>
+                  <c:v>1.2671671315003166</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.0376276820005526</c:v>
+                  <c:v>4.8149610153338864</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12.339547297800866</c:v>
+                  <c:v>11.7268806311342</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>25.571995554334666</c:v>
+                  <c:v>24.070662221001335</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>67.888637209599992</c:v>
+                  <c:v>62.613303876266663</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>126.06183587677722</c:v>
+                  <c:v>116.74405809899946</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>257.11469113353263</c:v>
+                  <c:v>228.81135780019932</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -825,28 +825,28 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>0.346481050900183</c:v>
+                  <c:v>0.32148105090018297</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.3363337981669832</c:v>
+                  <c:v>1.2671671315003166</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.0376276820005526</c:v>
+                  <c:v>4.8149610153338864</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12.339547297800866</c:v>
+                  <c:v>11.7268806311342</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>25.571995554334666</c:v>
+                  <c:v>24.070662221001335</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>67.888637209599992</c:v>
+                  <c:v>62.613303876266663</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>126.06183587677722</c:v>
+                  <c:v>116.74405809899946</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>257.11469113353263</c:v>
+                  <c:v>228.81135780019932</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1359,28 +1359,28 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>0.70756105979962691</c:v>
+                  <c:v>0.678561059799627</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.9451126259179166</c:v>
+                  <c:v>2.8142792925845832</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.613583485714358</c:v>
+                  <c:v>11.191440628571501</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>27.469421685714856</c:v>
+                  <c:v>26.465850257143426</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>58.774217379501856</c:v>
+                  <c:v>56.467788808073287</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>166.52270629566601</c:v>
+                  <c:v>159.32070629566599</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>300.11598233933267</c:v>
+                  <c:v>286.43998233933263</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>593.83995553493878</c:v>
+                  <c:v>562.47745553493883</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1880,28 +1880,28 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>0.70756105979962691</c:v>
+                  <c:v>0.678561059799627</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.9451126259179166</c:v>
+                  <c:v>2.8142792925845832</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.613583485714358</c:v>
+                  <c:v>11.191440628571501</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>27.469421685714856</c:v>
+                  <c:v>26.465850257143426</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>58.774217379501856</c:v>
+                  <c:v>56.467788808073287</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>166.52270629566601</c:v>
+                  <c:v>159.32070629566599</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>300.11598233933267</c:v>
+                  <c:v>286.43998233933263</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>593.83995553493878</c:v>
+                  <c:v>562.47745553493883</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5032,8 +5032,8 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <f t="shared" ref="G7:G14" si="1">C7/F7</f>
-        <v>0.346481050900183</v>
+        <f>E7/F7</f>
+        <v>0.32148105090018297</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -5057,8 +5057,8 @@
         <v>12</v>
       </c>
       <c r="G8">
-        <f t="shared" si="1"/>
-        <v>1.3363337981669832</v>
+        <f t="shared" ref="G8:G14" si="1">E8/F8</f>
+        <v>1.2671671315003166</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="G9">
         <f t="shared" si="1"/>
-        <v>5.0376276820005526</v>
+        <v>4.8149610153338864</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="G10">
         <f t="shared" si="1"/>
-        <v>12.339547297800866</v>
+        <v>11.7268806311342</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="G11">
         <f t="shared" si="1"/>
-        <v>25.571995554334666</v>
+        <v>24.070662221001335</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="G12">
         <f t="shared" si="1"/>
-        <v>67.888637209599992</v>
+        <v>62.613303876266663</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="G13">
         <f t="shared" si="1"/>
-        <v>126.06183587677722</v>
+        <v>116.74405809899946</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="G14">
         <f t="shared" si="1"/>
-        <v>257.11469113353263</v>
+        <v>228.81135780019932</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
@@ -5234,13 +5234,13 @@
         <v>5</v>
       </c>
       <c r="B19" s="4">
-        <v>0.346481050900183</v>
+        <v>0.32148105090018297</v>
       </c>
       <c r="G19">
         <v>120</v>
       </c>
       <c r="H19" s="4">
-        <v>0.346481050900183</v>
+        <v>0.32148105090018297</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
@@ -5248,13 +5248,13 @@
         <v>10</v>
       </c>
       <c r="B20" s="4">
-        <v>1.3363337981669832</v>
+        <v>1.2671671315003166</v>
       </c>
       <c r="G20">
         <v>240</v>
       </c>
       <c r="H20" s="4">
-        <v>1.3363337981669832</v>
+        <v>1.2671671315003166</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
@@ -5262,13 +5262,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="4">
-        <v>5.0376276820005526</v>
+        <v>4.8149610153338864</v>
       </c>
       <c r="G21">
         <v>480</v>
       </c>
       <c r="H21" s="4">
-        <v>5.0376276820005526</v>
+        <v>4.8149610153338864</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
@@ -5276,13 +5276,13 @@
         <v>32</v>
       </c>
       <c r="B22" s="4">
-        <v>12.339547297800866</v>
+        <v>11.7268806311342</v>
       </c>
       <c r="G22">
         <v>768</v>
       </c>
       <c r="H22" s="4">
-        <v>12.339547297800866</v>
+        <v>11.7268806311342</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
@@ -5290,13 +5290,13 @@
         <v>47</v>
       </c>
       <c r="B23" s="4">
-        <v>25.571995554334666</v>
+        <v>24.070662221001335</v>
       </c>
       <c r="G23">
         <v>1128</v>
       </c>
       <c r="H23" s="4">
-        <v>25.571995554334666</v>
+        <v>24.070662221001335</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
@@ -5304,13 +5304,13 @@
         <v>76</v>
       </c>
       <c r="B24" s="4">
-        <v>67.888637209599992</v>
+        <v>62.613303876266663</v>
       </c>
       <c r="G24">
         <v>1824</v>
       </c>
       <c r="H24" s="4">
-        <v>67.888637209599992</v>
+        <v>62.613303876266663</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
@@ -5318,13 +5318,13 @@
         <v>100</v>
       </c>
       <c r="B25" s="4">
-        <v>126.06183587677722</v>
+        <v>116.74405809899946</v>
       </c>
       <c r="G25">
         <v>2400</v>
       </c>
       <c r="H25" s="4">
-        <v>126.06183587677722</v>
+        <v>116.74405809899946</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
@@ -5332,13 +5332,13 @@
         <v>139</v>
       </c>
       <c r="B26" s="4">
-        <v>257.11469113353263</v>
+        <v>228.81135780019932</v>
       </c>
       <c r="G26">
         <v>3336</v>
       </c>
       <c r="H26" s="4">
-        <v>257.11469113353263</v>
+        <v>228.81135780019932</v>
       </c>
     </row>
   </sheetData>
@@ -5427,8 +5427,8 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <f t="shared" ref="G7:G14" si="1">C7/F7</f>
-        <v>0.70756105979962691</v>
+        <f>E7/F7</f>
+        <v>0.678561059799627</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -5452,8 +5452,8 @@
         <v>12</v>
       </c>
       <c r="G8">
-        <f t="shared" si="1"/>
-        <v>2.9451126259179166</v>
+        <f t="shared" ref="G8:G14" si="1">E8/F8</f>
+        <v>2.8142792925845832</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="G9">
         <f t="shared" si="1"/>
-        <v>11.613583485714358</v>
+        <v>11.191440628571501</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="G10">
         <f t="shared" si="1"/>
-        <v>27.469421685714856</v>
+        <v>26.465850257143426</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="G11">
         <f t="shared" si="1"/>
-        <v>58.774217379501856</v>
+        <v>56.467788808073287</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="G12">
         <f t="shared" si="1"/>
-        <v>166.52270629566601</v>
+        <v>159.32070629566599</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="G13">
         <f t="shared" si="1"/>
-        <v>300.11598233933267</v>
+        <v>286.43998233933263</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="G14">
         <f t="shared" si="1"/>
-        <v>593.83995553493878</v>
+        <v>562.47745553493883</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
@@ -5629,13 +5629,13 @@
         <v>5</v>
       </c>
       <c r="B19" s="4">
-        <v>0.70756105979962691</v>
+        <v>0.678561059799627</v>
       </c>
       <c r="G19">
         <v>215</v>
       </c>
       <c r="H19" s="4">
-        <v>0.70756105979962691</v>
+        <v>0.678561059799627</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
@@ -5643,13 +5643,13 @@
         <v>10</v>
       </c>
       <c r="B20" s="4">
-        <v>2.9451126259179166</v>
+        <v>2.8142792925845832</v>
       </c>
       <c r="G20">
         <v>430</v>
       </c>
       <c r="H20" s="4">
-        <v>2.9451126259179166</v>
+        <v>2.8142792925845832</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
@@ -5657,13 +5657,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="4">
-        <v>11.613583485714358</v>
+        <v>11.191440628571501</v>
       </c>
       <c r="G21">
         <v>860</v>
       </c>
       <c r="H21" s="4">
-        <v>11.613583485714358</v>
+        <v>11.191440628571501</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
@@ -5671,13 +5671,13 @@
         <v>32</v>
       </c>
       <c r="B22" s="4">
-        <v>27.469421685714856</v>
+        <v>26.465850257143426</v>
       </c>
       <c r="G22">
         <v>1376</v>
       </c>
       <c r="H22" s="4">
-        <v>27.469421685714856</v>
+        <v>26.465850257143426</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
@@ -5685,13 +5685,13 @@
         <v>47</v>
       </c>
       <c r="B23" s="4">
-        <v>58.774217379501856</v>
+        <v>56.467788808073287</v>
       </c>
       <c r="G23">
         <v>2021</v>
       </c>
       <c r="H23" s="4">
-        <v>58.774217379501856</v>
+        <v>56.467788808073287</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
@@ -5699,13 +5699,13 @@
         <v>76</v>
       </c>
       <c r="B24" s="4">
-        <v>166.52270629566601</v>
+        <v>159.32070629566599</v>
       </c>
       <c r="G24">
         <v>3268</v>
       </c>
       <c r="H24" s="4">
-        <v>166.52270629566601</v>
+        <v>159.32070629566599</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
@@ -5713,13 +5713,13 @@
         <v>100</v>
       </c>
       <c r="B25" s="4">
-        <v>300.11598233933267</v>
+        <v>286.43998233933263</v>
       </c>
       <c r="G25">
         <v>4300</v>
       </c>
       <c r="H25" s="4">
-        <v>300.11598233933267</v>
+        <v>286.43998233933263</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
@@ -5727,13 +5727,13 @@
         <v>139</v>
       </c>
       <c r="B26" s="4">
-        <v>593.83995553493878</v>
+        <v>562.47745553493883</v>
       </c>
       <c r="G26">
         <v>5977</v>
       </c>
       <c r="H26" s="4">
-        <v>593.83995553493878</v>
+        <v>562.47745553493883</v>
       </c>
     </row>
   </sheetData>
